--- a/01_data/01_input_data/02_processed/Data_update.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956BC99B-CC08-461C-A882-7AC084647258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDADD97-C42D-4DED-B861-4FF8FEC56B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -18,7 +18,6 @@
     <sheet name="Edges" sheetId="3" r:id="rId3"/>
     <sheet name="Parameters" sheetId="4" r:id="rId4"/>
     <sheet name="Supply" sheetId="5" r:id="rId5"/>
-    <sheet name="Demand" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="28">
   <si>
     <t>S1</t>
   </si>
@@ -95,9 +94,6 @@
   </si>
   <si>
     <t>Supply</t>
-  </si>
-  <si>
-    <t>Demand</t>
   </si>
   <si>
     <t>D5</t>
@@ -490,7 +486,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -530,32 +526,32 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -575,12 +571,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -662,7 +658,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -670,47 +666,47 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
         <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -749,12 +745,12 @@
         <v>15</v>
       </c>
       <c r="I1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
@@ -783,7 +779,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -812,7 +808,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -841,7 +837,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -870,7 +866,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -899,7 +895,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -928,7 +924,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -957,13 +953,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>500</v>
@@ -986,13 +982,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10">
         <v>500</v>
@@ -1015,13 +1011,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
         <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
       </c>
       <c r="D11">
         <v>500</v>
@@ -1044,13 +1040,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <v>500</v>
@@ -1073,13 +1069,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13">
         <v>500</v>
@@ -1102,13 +1098,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
         <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
       </c>
       <c r="D14">
         <v>500</v>
@@ -1131,13 +1127,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>500</v>
@@ -1160,7 +1156,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
         <v>0</v>
@@ -1189,7 +1185,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
         <v>0</v>
@@ -1218,7 +1214,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
         <v>1</v>
@@ -1247,7 +1243,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
@@ -1276,7 +1272,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -1305,7 +1301,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -1334,7 +1330,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
@@ -1363,13 +1359,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D23">
         <v>500</v>
@@ -1392,13 +1388,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24">
         <v>500</v>
@@ -1421,13 +1417,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
         <v>20</v>
-      </c>
-      <c r="C25" t="s">
-        <v>21</v>
       </c>
       <c r="D25">
         <v>500</v>
@@ -1450,13 +1446,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D26">
         <v>500</v>
@@ -1479,13 +1475,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D27">
         <v>500</v>
@@ -1508,13 +1504,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
         <v>23</v>
-      </c>
-      <c r="C28" t="s">
-        <v>24</v>
       </c>
       <c r="D28">
         <v>500</v>
@@ -1537,13 +1533,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29">
         <v>500</v>
@@ -1588,7 +1584,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
@@ -1599,7 +1595,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -1610,7 +1606,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -1621,7 +1617,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
@@ -1632,7 +1628,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -1643,7 +1639,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -1654,7 +1650,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -1665,7 +1661,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -1676,7 +1672,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
@@ -1687,7 +1683,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -1698,10 +1694,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12">
         <v>-20</v>
@@ -1709,10 +1705,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13">
         <v>-5</v>
@@ -1720,10 +1716,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14">
         <v>-5</v>
@@ -1731,10 +1727,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <v>-10</v>
@@ -1742,10 +1738,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16">
         <v>-10</v>
@@ -1753,10 +1749,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17">
         <v>-5</v>
@@ -1764,7 +1760,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -1775,7 +1771,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
@@ -1786,7 +1782,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
@@ -1797,7 +1793,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
@@ -1808,10 +1804,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22">
         <v>-20</v>
@@ -1819,10 +1815,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23">
         <v>-5</v>
@@ -1830,10 +1826,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24">
         <v>-5</v>
@@ -1841,10 +1837,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25">
         <v>-10</v>
@@ -1852,10 +1848,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26">
         <v>-10</v>
@@ -1863,253 +1859,12 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27">
-        <v>-5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41A9F00-9629-4966-93BA-5527DE59CE88}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21">
         <v>-5</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/Data_update.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDADD97-C42D-4DED-B861-4FF8FEC56B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A005AA91-038E-4FF9-A55F-F60EFAE237D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>

--- a/01_data/01_input_data/02_processed/Data_update.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A005AA91-038E-4FF9-A55F-F60EFAE237D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669F8AED-89A4-4752-8F26-3CBA26571D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>

--- a/01_data/01_input_data/02_processed/Data_update.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669F8AED-89A4-4752-8F26-3CBA26571D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB5F6F3-D612-40F9-BF71-3716FB7E0E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>

--- a/01_data/01_input_data/02_processed/Data_update.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB5F6F3-D612-40F9-BF71-3716FB7E0E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D20B0F-9124-42F1-8BC3-38155DD48764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-5070" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -1601,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1634,7 +1634,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">

--- a/01_data/01_input_data/02_processed/Data_update.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D20B0F-9124-42F1-8BC3-38155DD48764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C31F195-39CA-4D76-8A32-E81E4AE03078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-5070" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -1711,7 +1711,7 @@
         <v>19</v>
       </c>
       <c r="C13">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">

--- a/01_data/01_input_data/02_processed/Data_update.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C31F195-39CA-4D76-8A32-E81E4AE03078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB356B6F-766F-4F18-A8F2-97277EE6B7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5070" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>

--- a/01_data/01_input_data/02_processed/Data_update.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB356B6F-766F-4F18-A8F2-97277EE6B7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3607DD-2064-45FC-B483-AD4F3C3E5AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -1601,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1634,7 +1634,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>60</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">

--- a/01_data/01_input_data/02_processed/Data_update.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3607DD-2064-45FC-B483-AD4F3C3E5AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F9600D-2063-4837-B08E-B90595B154E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
